--- a/docs/COLLABORATION.xlsx
+++ b/docs/COLLABORATION.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="612" yWindow="504" windowWidth="21792" windowHeight="8652"/>
+    <workbookView xWindow="420" yWindow="528" windowWidth="37632" windowHeight="12540" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="영역 분류" sheetId="1" r:id="rId1"/>
     <sheet name="AI 작업 룰" sheetId="2" r:id="rId2"/>
-    <sheet name="배경 — 발견의 흐름" sheetId="3" r:id="rId3"/>
+    <sheet name="CLAUDE.md 작성 가이드" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="71">
   <si>
     <t>분류</t>
   </si>
@@ -57,6 +57,9 @@
     <t>AI 채팅</t>
   </si>
   <si>
+    <t>frontend/src/features/chat, features/ai-assistant</t>
+  </si>
+  <si>
     <t>사용자/인증 화면</t>
   </si>
   <si>
@@ -81,6 +84,9 @@
     <t>frontend/src/features/settings</t>
   </si>
   <si>
+    <t>인프라 공통 — UI/흐름</t>
+  </si>
+  <si>
     <t>글로벌 상태</t>
   </si>
   <si>
@@ -96,7 +102,7 @@
     <t>디자인 토큰</t>
   </si>
   <si>
-    <t>frontend/src/shared/constants/ (colors, spacing, themes 등)</t>
+    <t>frontend/src/shared/constants/ (colors, spacing, themes)</t>
   </si>
   <si>
     <t>공통 타입</t>
@@ -150,137 +156,153 @@
     <t>누구든</t>
   </si>
   <si>
+    <t>커스텀 훅</t>
+  </si>
+  <si>
+    <t>frontend/src/shared/hooks/ (useTheme, useResponsive 등)</t>
+  </si>
+  <si>
+    <t>룰</t>
+  </si>
+  <si>
+    <t>설명</t>
+  </si>
+  <si>
+    <t>영역 외 작업 금지</t>
+  </si>
+  <si>
+    <t>인프라 변경 시 알림</t>
+  </si>
+  <si>
+    <t>대상</t>
+  </si>
+  <si>
+    <t>박을 내용 (그대로 복붙 가능)</t>
+  </si>
+  <si>
+    <t>양쪽 공통
+(프로젝트 CLAUDE.md 또는 양쪽 개인 CLAUDE.md에 같은 내용)</t>
+  </si>
+  <si>
+    <t>자기 할거 하면 됨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>민기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>큰 변경 시 알려주기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가는 자유. 큰 변경 시 알려주기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>큰 변경시 알려주기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>혁준</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERD 수시 참조</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>추가는 자유. 수정/삭제는 영향 검토</t>
-  </si>
-  <si>
-    <t>커스텀 훅</t>
-  </si>
-  <si>
-    <t>frontend/src/shared/hooks/ (useTheme, useResponsive 등)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>추가는 자유</t>
-  </si>
-  <si>
-    <t>룰</t>
-  </si>
-  <si>
-    <t>설명</t>
-  </si>
-  <si>
-    <t>영역 외 작업 금지</t>
-  </si>
-  <si>
-    <t>AI는 사용자가 지정한 영역 외 다른 영역(특히 자기 강점 아닌 인프라 공통)을 만지기 전 반드시 사용자에게 확인</t>
-  </si>
-  <si>
-    <t>작업 시작 한 줄 강조</t>
-  </si>
-  <si>
-    <t>사용자는 큰 작업 시작 시 한 줄로 영역 명시 (예: "이번엔 features/board만 만져, 다른 곳 손대지 마")</t>
-  </si>
-  <si>
-    <t>인프라 변경 시 알림</t>
-  </si>
-  <si>
-    <t>인프라 공통에 변경이 있는 작업은 완료 후 동료에게 한 줄 알림 (변경 영역 + 의도)</t>
-  </si>
-  <si>
-    <t>AI에게 git 머지 위임 금지</t>
-  </si>
-  <si>
-    <t>git 머지/리베이스/충돌 해결은 인간이 직접. AI는 잘 못함 (실험적으로 확인됨)</t>
-  </si>
-  <si>
-    <t>트렁크 기반 + 작은 PR</t>
-  </si>
-  <si>
-    <t>main에 자주 머지. 3시간 이상 살아있는 브랜치 위험. 작업 단위는 작게 쪼개기</t>
-  </si>
-  <si>
-    <t>단계</t>
-  </si>
-  <si>
-    <t>발견</t>
-  </si>
-  <si>
-    <t>1. 현 상황 진단</t>
-  </si>
-  <si>
-    <t>충돌 사고 0건. 단 인적 노력(디렉토리 분리 + 매번 대화)으로 막는 중 — 지속 불가, 시한폭탄. 사고 나기 전에 손대는 게 정확한 시점.</t>
-  </si>
-  <si>
-    <t>2. 인적 노력의 두 종류</t>
-  </si>
-  <si>
-    <t>A(작업 전 영역 분리) vs B(작업 중 대화). B가 진짜 부담. A는 한 번 잘 잡으면 두고두고 편함.</t>
-  </si>
-  <si>
-    <t>3. 통합정보 PL 모델</t>
-  </si>
-  <si>
-    <t>PL이 ① 영역 정의 → ② 문서로 박기 → ③ 작업자가 보면 0초만에 안다. A를 잘 잡으면 B가 자동으로 줄어든다.</t>
-  </si>
-  <si>
-    <t>4. 영역 단위 결정</t>
-  </si>
-  <si>
-    <t>프론트/백 분리는 적합하지 않음. 도메인(features/{게시판,결재,...}) 기준이 자연스럽다. 단 '공통'이 애매하다는 발견.</t>
-  </si>
-  <si>
-    <t>5. 공통의 두 종류</t>
-  </si>
-  <si>
-    <t>유틸 공통(추가형 — 안전) vs 인프라 공통(기반형 — 위험). 업계 표준 용어로는 'Stable vs Volatile dependencies' 등.</t>
-  </si>
-  <si>
-    <t>6. 인프라 공통의 분리</t>
-  </si>
-  <si>
-    <t>한 명 게이트키퍼는 강점이 다른 우리에겐 안 맞음. UI/흐름(사장 강점) vs 보안/백엔드(동료 강점)으로 자연 분담.</t>
-  </si>
-  <si>
-    <t>7. AI 시대의 추가 위험</t>
-  </si>
-  <si>
-    <t>인간끼리는 강점 따라 자연 분담. 진짜 문제는 AI가 영역을 안 지킬 때 (예: executor가 사양에 없는 NavRailMorePopover 자의 정리).</t>
-  </si>
-  <si>
-    <t>8. 해결책</t>
-  </si>
-  <si>
-    <t>CLAUDE.md에 영역 룰 박기 + 큰 작업 시작 시 한 줄 강조. PR 리뷰는 자연스럽게.</t>
-  </si>
-  <si>
-    <t>frontend/src/features/chat, features/ai-assistant</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>기능별 작업시 각자 진행하면 됨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>민기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>혁준</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>알아서 하되, 큰 변경 시 간단히 알림</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>추가는 자유. 토큰 의미 변경은 동료 알림</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>알려주면 좋지만 알아서 추적하게 될 것임</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>인프라 공통 — UI/UX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI는 사용자가 지정한 영역 외 다른 영역을 만지기 전 반드시 사용자에게 확인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>인프라 공통에 변경이 있는 작업은 완료 후 알려주기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">## 협업 구조
+### 영역 분류
+- **도메인 (자유 영역)**
+  - frontend/src/features/{board, approval, report, chat, users, settings, notifications, admin-*}
+  - backend/.../domain/{post, approval, report, user}
+  - 자기 도메인 작업 시 매번 알림 불필요
+- **인프라 공통 — UI/흐름 (민기)**
+  - frontend/src/store/uiStore.ts
+  - frontend/src/layout/
+  - frontend/src/shared/constants/
+  - frontend/src/types/index.ts
+- **인프라 공통 — 보안/백엔드 (혁준)**
+  - backend/.../security/
+  - backend/.../config/
+  - backend/src/main/resources/application*.yml
+  - backend/.../common/
+  - frontend/src/features/auth/api.ts
+  - frontend/src/shared/api/client.ts
+- **유틸 공통 (누구든 자유롭게 추가 가능)**
+  - frontend/src/shared/components/
+  - frontend/src/shared/hooks/
+### AI 작업 룰
+1. 영역 외 작업 금지 — 자기 영역 아닌 영역을 만지기 전에는 반드시 사용자에게 확인.
+2. 인프라 변경 시 알림 — 인프라 공통에 변경이 있는 작업은 완료 후 알려주기.
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>민기의 CLAUDE.md에 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>## 나의 작업 컨텍스트 (민기)
+- 나의 영역: **인프라 공통 — UI/흐름**
+- 자주 만지는 곳:
+  - frontend/src/store/uiStore.ts
+  - frontend/src/layout/ (NavRail, TopHeader, MobileApp 등)
+  - frontend/src/shared/constants/
+- 도메인 작업은 분담되는대로 각자 알아서 진행하면 됨. 충돌 확률 낮음.
+### 영역 침범 방지
+다른 영역(보안/백엔드 인프라)을 만지기 전:
+- 작업 사양에 명시되지 않은 한 손대지 말 것.
+- 사용자가 동료와 사전 협의 후 명시할 때만 작업.
+- 의식적으로 피할 경로:
+  - backend/.../security/
+  - backend/.../config/
+  - backend/src/main/resources/application*.yml
+  - frontend/src/features/auth/api.ts
+  - frontend/src/shared/api/client.ts
+  - DB 스키마 (INT_USER, INT_RF_TK 등)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>혁준의 CLAUDE.md에 추가</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>## 나의 작업 컨텍스트 (혁준)
+- 나의 강점 영역: **인프라 공통 — 보안/백엔드**
+- 자주 만지는 곳:
+  - backend/.../security/
+  - backend/.../config/, application*.yml
+  - backend/.../common/ (BaseEntity 등)
+  - frontend/src/features/auth/api.ts
+  - frontend/src/shared/api/client.ts
+- DB 스키마 게이트키퍼 — INT_USER, INT_RF_TK, INT_DEPT, INT_JBGD, INT_COM_CODE 등.
+### 영역 침범 방지
+다른 영역(UI/흐름 인프라)을 만지기 전:
+- 작업 사양에 명시되지 않은 한 손대지 말 것.
+- 사용자가 사장과 사전 협의 후 명시할 때만 작업.
+- 의식적으로 피할 경로:
+  - frontend/src/store/uiStore.ts
+  - frontend/src/layout/
+  - frontend/src/shared/constants/
+  - frontend/src/types/index.ts</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -312,7 +334,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -349,6 +371,12 @@
         <bgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -362,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -380,6 +408,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -720,7 +751,7 @@
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -735,7 +766,7 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
@@ -750,7 +781,7 @@
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
@@ -761,11 +792,11 @@
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -773,14 +804,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -788,14 +819,14 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
@@ -803,14 +834,14 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
@@ -818,201 +849,201 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="E20" s="5" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1024,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1039,131 +1070,68 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="25.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="31.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="6" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="348" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B5" s="6" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="348" x14ac:dyDescent="0.4">
+      <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="34.799999999999997" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>
